--- a/src/abap/snapshot/הקמת_טבלה_ILG_MM_GP_TRK.xlsx
+++ b/src/abap/snapshot/הקמת_טבלה_ILG_MM_GP_TRK.xlsx
@@ -473,19 +473,14 @@
           <t>הקמת טבלה /ILG/MM_GP_TRK - הנחיות מלאות</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>שלב 1 - יצירה</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,17 +530,13 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>שלב 2 - מאפיינים כלליים</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -583,17 +574,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>שלב 3 - Technical Settings (כפתור בסרגל)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -643,17 +630,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>שלב 4 - Enhancement Category</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -679,17 +662,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>שלב 5 - שדות</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -703,17 +682,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>שלב 6 - שמירה והפעלה</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -739,17 +714,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>שלב 7 - אחרי ההקמה</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -895,7 +866,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LOGICAL_STATUS_CODE</t>
+          <t>STATUS_CODE</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -1011,7 +982,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>MBLNR_HANDLED_MANUALLY</t>
+          <t>MBLNR_MANUAL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
